--- a/waveprocessed/PROCESSED-20251113-tett6roof/meta.xlsx
+++ b/waveprocessed/PROCESSED-20251113-tett6roof/meta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DF2"/>
+  <dimension ref="A1:DF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,27 +944,27 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>PROCESSED_folder</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
           <t>Probe 1 Frequency (FFT)</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>Probe 2 Frequency (FFT)</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>Probe 3 Frequency (FFT)</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>Probe 4 Frequency (FFT)</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>PROCESSED_folder</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
         <v>18000</v>
       </c>
       <c r="O2" t="n">
-        <v>268.59176</v>
+        <v>268.57</v>
       </c>
       <c r="P2" t="n">
         <v>3950</v>
@@ -1054,13 +1054,13 @@
         <v>1.5385</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.048927717267305</v>
+        <v>2.048927717267306</v>
       </c>
       <c r="Z2" t="n">
         <v>3.066572458475788</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.368190619240341</v>
+        <v>5.368190619240342</v>
       </c>
       <c r="AB2" t="n">
         <v>0.02902306111509137</v>
@@ -1077,7 +1077,7 @@
         <v>9455</v>
       </c>
       <c r="AH2" t="n">
-        <v>269.05736</v>
+        <v>268.99</v>
       </c>
       <c r="AI2" t="n">
         <v>4000</v>
@@ -1107,16 +1107,16 @@
         <v>1.5385</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.048927717267305</v>
+        <v>2.048927717267306</v>
       </c>
       <c r="AS2" t="n">
         <v>3.066572458475788</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.368190619240341</v>
+        <v>5.368190619240342</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.02911526286236843</v>
+        <v>0.02911526286236844</v>
       </c>
       <c r="AV2" t="n">
         <v>0.8300751689623258</v>
@@ -1130,7 +1130,7 @@
         <v>12544</v>
       </c>
       <c r="BA2" t="n">
-        <v>269.80872</v>
+        <v>269.77</v>
       </c>
       <c r="BB2" t="n">
         <v>4500</v>
@@ -1160,16 +1160,16 @@
         <v>1.5385</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.048927717267305</v>
+        <v>2.048927717267306</v>
       </c>
       <c r="BL2" t="n">
         <v>3.066572458475788</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.368190619240341</v>
+        <v>5.368190619240342</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.02920746460964543</v>
+        <v>0.02920746460964544</v>
       </c>
       <c r="BO2" t="n">
         <v>0.8300751689623258</v>
@@ -1183,7 +1183,7 @@
         <v>12545</v>
       </c>
       <c r="BT2" t="n">
-        <v>270.19496</v>
+        <v>270.2</v>
       </c>
       <c r="BU2" t="n">
         <v>4500</v>
@@ -1213,16 +1213,16 @@
         <v>1.5385</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.048927717267305</v>
+        <v>2.048927717267306</v>
       </c>
       <c r="CE2" t="n">
         <v>3.066572458475788</v>
       </c>
       <c r="CF2" t="n">
-        <v>5.368190619240341</v>
+        <v>5.368190619240342</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.02910501822378207</v>
+        <v>0.02910501822378208</v>
       </c>
       <c r="CH2" t="n">
         <v>0.8300751689623258</v>
@@ -1270,8 +1270,10 @@
       <c r="DA2" t="n">
         <v>1.002721033625528</v>
       </c>
-      <c r="DB2" t="n">
-        <v>0.6499837504062399</v>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
       </c>
       <c r="DC2" t="n">
         <v>0.6499837504062399</v>
@@ -1282,10 +1284,2886 @@
       <c r="DE2" t="n">
         <v>0.6499837504062399</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DF2" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-nowind-amp0100-freq0650-per40-depth580-mstop30-run1.csv</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:26:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40</v>
+      </c>
+      <c r="K3" t="n">
+        <v>580</v>
+      </c>
+      <c r="L3" t="n">
+        <v>30</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3950</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>13180.76923076923</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4.849999999999994</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.46473682383476</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4.470958810408151</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6.330741926478114</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1389036475183248</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.332265594790045</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.048927717267306</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.066572458475788</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.368190619240342</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.009937299428746422</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8300751689623258</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.993222267452576</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>13230.76923076923</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>5.109999999999985</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4.764172512009643</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4.780234455321449</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>6.769516667500678</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.2870346892296441</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6.775599222533063</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.048927717267306</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.066572458475788</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.368190619240342</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.0104700206352359</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.8300751689623258</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.993222267452576</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>13730.76923076923</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.685000000000031</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.529616432010443</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>4.534792249990878</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>6.420427419951952</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0.1366299096744683</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>6.421881031838609</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>2.048927717267306</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>3.066572458475788</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>5.368190619240342</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.009599226355397393</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.8300751689623258</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1.993222267452576</v>
+      </c>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>13730.76923076923</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>4.889999999999986</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>4.55845385710621</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>4.567881665772925</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>6.464856738559091</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.1209979828152048</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>6.465988954671841</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>2.048927717267306</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>3.066572458475788</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>5.368190619240342</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.0100192565374371</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.8300751689623258</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>1.993222267452576</v>
+      </c>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="n">
+        <v>2.048998605091</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>3.066466366335344</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>5.368376345338421</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0.01047038287201498</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>1.18841919095278</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0.8300879542525339</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>1.993203138117973</v>
+      </c>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="n">
+        <v>1.067066817147287</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>0.9507666694671687</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>1.00636641656719</v>
+      </c>
+      <c r="DB3" t="inlineStr">
         <is>
           <t>PROCESSED-20251113-tett6roof</t>
         </is>
+      </c>
+      <c r="DC3" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-nowind-amp0200-freq1300-per40-depth580-mstop30-run1.csv</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:10:22</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" t="n">
+        <v>580</v>
+      </c>
+      <c r="L4" t="n">
+        <v>30</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4700</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9315.384615384615</v>
+      </c>
+      <c r="R4" t="n">
+        <v>16.782</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15.47118888520432</v>
+      </c>
+      <c r="T4" t="n">
+        <v>15.63633054529925</v>
+      </c>
+      <c r="U4" t="n">
+        <v>22.1604006437392</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.790068380971786</v>
+      </c>
+      <c r="W4" t="n">
+        <v>22.23258198004882</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1142291869391728</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>9415.384615384615</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>16.95662500000003</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>15.60483756739707</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>15.63571286140404</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>22.16823773450984</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.796019688892619</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>22.24087343106461</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.115417798056397</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>11.72000000000003</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>10.16099133249193</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>9.982052026791816</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>14.1481755937165</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.9819887676947914</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>14.18221331705718</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.0797739286692354</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>11.97500000000002</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>10.57923493858625</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>10.42531591863569</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>14.78683263613222</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.538181810275313</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>14.86662109191079</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.08150962421621959</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="n">
+        <v>6.80845382890728</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.922850542145485</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>17.83814903173707</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0.1154483984065951</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>3.948903220766222</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.9992571606462729</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>1.19970570478913</v>
+      </c>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="n">
+        <v>1.008638552808347</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.6511436782732762</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1.041161693028602</v>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="DC4" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>1.299826689774697</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-nowind-amp0100-freq1300-per40-depth580-mstop30-run1.csv</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:08:06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40</v>
+      </c>
+      <c r="K5" t="n">
+        <v>580</v>
+      </c>
+      <c r="L5" t="n">
+        <v>30</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4700</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>9315.384615384615</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8.414999999999992</v>
+      </c>
+      <c r="S5" t="n">
+        <v>7.823183711811956</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7.732526771658283</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10.96242803326361</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.021131359922834</v>
+      </c>
+      <c r="W5" t="n">
+        <v>11.00988363420349</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.05727795305047898</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>9415.384615384615</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>8.539999999999992</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>7.512481246199147</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>7.623165263513712</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>10.81554678132595</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.334633275989068</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>10.8975822162729</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.05812878420096144</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.724999999999994</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.323150470516596</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.350858132791348</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6.159907147638667</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.3547009822265755</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>6.170110927229951</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.03216141748823686</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>4.940000000000026</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>4.516689190015959</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>4.550798463013243</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>6.443504927646345</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.3992269192931915</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>6.455860739335312</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.0336248470670669</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="n">
+        <v>6.80845382890728</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0.922850542145485</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>17.83814903173707</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.05814419569886811</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>3.948903220766222</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.9992571606462729</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>1.19970570478913</v>
+      </c>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="n">
+        <v>0.9602843960900866</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.5754623976870283</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>1.044767981318086</v>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="DC5" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.299826689774697</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-nowind-amp0200-freq0650-per40-depth580-mstop30-run1.csv</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:23:28</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K6" t="n">
+        <v>580</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3950</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13180.76923076923</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9.490000000000009</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8.888370382137218</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8.902653780747572</v>
+      </c>
+      <c r="U6" t="n">
+        <v>12.60745131773329</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.2615054453026831</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12.61016311658726</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.048927717267306</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.066572458475788</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.368190619240342</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.01944432403686675</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.8300751689623258</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.993222267452576</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>13230.76923076923</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>9.659999999999997</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>9.320232764156783</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>9.349100963432806</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>13.23596131692082</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.3187290227860898</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13.23979834336575</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.048927717267306</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.066572458475788</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.368190619240342</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.01979264174880217</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.8300751689623258</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.993222267452576</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>13730.76923076923</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9.445000000000022</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>8.998638508131421</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>9.020517659632313</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>12.76893679099696</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.2479633341126553</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>12.77134419658088</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2.048927717267306</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>3.066572458475788</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>5.368190619240342</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.01935212228958975</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.8300751689623258</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.993222267452576</v>
+      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>4500</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>13730.76923076923</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>9.615000000000009</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>9.03487340262007</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>9.056478451834783</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>12.82214090567734</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.237999349226677</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>12.82434953887629</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>1.5385</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>2.048927717267306</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>3.066572458475788</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>5.368190619240342</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.01970044000152517</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.8300751689623258</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>1.993222267452576</v>
+      </c>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="n">
+        <v>2.048998605091</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>3.066466366335344</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>5.368376345338421</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.01979332652517905</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>1.18841919095278</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.8300879542525339</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>1.993203138117973</v>
+      </c>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="n">
+        <v>1.048587352175093</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.9654950402888938</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>1.004026708535509</v>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.6499837504062399</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-nowind-nowave-freq1300-per40-depth580-mstop30-run1.csv</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:06:28</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" t="n">
+        <v>580</v>
+      </c>
+      <c r="L7" t="n">
+        <v>30</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O7" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4700</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>9315.384615384615</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.04499999999998749</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.001121612569711128</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.002756446477178402</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.005718307937832363</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.01570310632939529</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.01671186985541029</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.9232</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.761201086064131</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.319663923788107</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>12.47434684548802</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.0002142540488728263</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.992044024522438</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.429445324727152</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>9415.384615384615</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.2200000000000273</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.01383000732085631</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.02857499214500419</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.08837479428376437</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1367816149230967</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.1628475190037232</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.025777777777778</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.908915257338599</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.60739870105486</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.24135797422713</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.0008599613566145985</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.9787600468623101</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.567004799555214</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.04499999999998749</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.005744110784569817</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.01174336482107343</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.02343183180151267</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.04575235388411374</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.05140358574566133</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.8792380952380952</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.231619913490253</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.20100187151933</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>13.70684417334446</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.0002354228961069959</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.9953822304573618</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1.365957501186412</v>
+      </c>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.08500000000000796</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.002129431812910728</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.004436194125615608</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.009149683148973494</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.01827654582425401</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.02043890478946135</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.6838518518518518</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>8.609044975343432</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.7298353447072029</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>22.55569783539979</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.0007317688229042602</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.9999079695453716</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.067241892715255</v>
+      </c>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="n">
+        <v>6.80845382890728</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.922850542145485</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>17.83814903173707</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.001497859842359787</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>3.948903220766222</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.9992571606462729</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>1.19970570478913</v>
+      </c>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="n">
+        <v>12.33046748434553</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.4153367855349886</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.3707156586587672</v>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="DC7" t="n">
+        <v>1.083188908145581</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.9748700173310225</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1.13734835355286</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1.462305025996534</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-nowind-amp0300-freq1300-per40-depth580-mstop30-run1.csv</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:13:10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>40</v>
+      </c>
+      <c r="K8" t="n">
+        <v>580</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O8" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4700</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9315.384615384615</v>
+      </c>
+      <c r="R8" t="n">
+        <v>26.14162499999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22.75401383226536</v>
+      </c>
+      <c r="T8" t="n">
+        <v>22.73657371653815</v>
+      </c>
+      <c r="U8" t="n">
+        <v>32.35148773854499</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.735122399204909</v>
+      </c>
+      <c r="W8" t="n">
+        <v>32.69617933387138</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1779368709938478</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>9415.384615384615</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>24.59662500000002</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>22.52843153723217</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>22.35088360837119</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>31.66707841846137</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.093391488865637</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>31.73619610927933</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.1674205979738847</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>18.02999999999999</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>15.9102117780071</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>15.97960807881907</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>22.65377377393175</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1.885899445029984</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>22.73213766712762</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.7691666666666667</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>6.809582094531432</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.9226976369409542</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>17.84110508767235</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.1227767651644016</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.9992581318692667</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1.199606895264513</v>
+      </c>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>18.37500000000001</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>16.15787893864201</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>16.27760005290235</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>23.14735346006549</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>3.892179268298839</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>23.47230350139886</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.7691666666666667</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>6.809582094531432</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.9226976369409542</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>17.84110508767235</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.1251260709870152</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.9992581318692667</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1.199606895264513</v>
+      </c>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="n">
+        <v>6.80845382890728</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0.922850542145485</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>17.83814903173707</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.1674649856594466</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>3.948903220766222</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0.9992571606462729</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>1.19970570478913</v>
+      </c>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="n">
+        <v>0.990086043864783</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0.706228116756051</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>1.015566553361487</v>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="DC8" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>1.300108342361864</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.300108342361864</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-lowestwind-amp0100-freq1300-per40-depth580-mstop30-run2.csv</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:35:12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>lowest</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>40</v>
+      </c>
+      <c r="K9" t="n">
+        <v>580</v>
+      </c>
+      <c r="L9" t="n">
+        <v>30</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O9" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4700</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9315.384615384615</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8.585000000000008</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7.529046565807</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.545058653798318</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10.69182250769127</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.329074950945369</v>
+      </c>
+      <c r="W9" t="n">
+        <v>10.7741128990374</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.05843508341513523</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>9415.384615384615</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>9.274999999999977</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>7.695264194023932</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>7.698276320933147</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>10.92079591841597</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.587495671408587</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11.03557547201015</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.0631316713657982</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.748125000000005</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.298652906865373</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4.342452515563213</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.149376937053908</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.411396388871564</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>6.163122885578955</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.03231882125107619</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>5.164999999999992</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>4.473551514851751</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>4.455187438226599</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>6.311389941111753</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.5629158935460172</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>6.336443583902039</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.03515634313793509</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="n">
+        <v>6.80845382890728</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.922850542145485</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>17.83814903173707</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.06314840926311487</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>3.948903220766222</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.9992571606462729</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>1.19970570478913</v>
+      </c>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="n">
+        <v>1.022076849540525</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.558610178738719</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1.04068684115134</v>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="DC9" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1.299826689774697</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-lowestwind-amp0100-freq1300-per40-depth580-mstop30-run3.csv</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:37:22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>lowest</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" t="n">
+        <v>580</v>
+      </c>
+      <c r="L10" t="n">
+        <v>30</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O10" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4700</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9315.384615384615</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8.844999999999999</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7.495042445971214</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7.542812715994216</v>
+      </c>
+      <c r="U10" t="n">
+        <v>10.69454968049252</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.342666462164123</v>
+      </c>
+      <c r="W10" t="n">
+        <v>10.77850388955457</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.06020481220813868</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>9415.384615384615</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>9.486625000000036</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>7.713028804294415</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>7.770804522504227</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>11.02405027167653</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.42866321706439</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11.11623870651598</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.06457212850356539</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.810000000000002</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.270011258334289</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.273563857763413</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>6.051283060824218</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.4257562133370325</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>6.066242249977594</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.03273998267056498</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>5.23662500000001</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>4.508922816863958</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>4.528138126810433</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>6.411957148108566</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.515222658491856</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>6.432623792590698</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.03564386938716167</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="n">
+        <v>6.80845382890728</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.922850542145485</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>17.83814903173707</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.06458924830465776</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>3.948903220766222</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.9992571606462729</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>1.19970570478913</v>
+      </c>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="n">
+        <v>1.029084072557904</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.5536101791758975</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.05595103714618</v>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="DC10" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.299826689774697</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>/Users/ole/Kodevik/wave_project/wavedata/20251113-tett6roof/reversepanel-lowestwind-amp0100-freq1300-per40-depth580-mstop30-run1.csv</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-11-13T13:33:30</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lowest</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>reverse</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" t="n">
+        <v>580</v>
+      </c>
+      <c r="L11" t="n">
+        <v>30</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>18000</v>
+      </c>
+      <c r="O11" t="n">
+        <v>268.57</v>
+      </c>
+      <c r="P11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9315.384615384615</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9.012000000000015</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7.589700787973445</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7.562621054090918</v>
+      </c>
+      <c r="U11" t="n">
+        <v>10.72438278779763</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.561865129429895</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10.83751857492014</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.06134152262518336</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="n">
+        <v>9455</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>268.99</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4800</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>9415.384615384615</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>9.405000000000001</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>7.648529647173817</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>7.694005679415478</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>10.91015345161025</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.660343388709633</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>11.03576859607499</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.06401653576230011</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>12544</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.679999999999978</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.208029538591402</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.232413634891929</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.994004366084904</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.4165074893586085</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>6.008457941047496</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.03185511827406306</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="n">
+        <v>12545</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>270.2</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>6500</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>11115.38461538462</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>5.194999999999993</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>4.440112917778618</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>4.406550680851361</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>6.240463752562203</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.5814766837244281</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>6.267495750358184</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.7693333333333332</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>6.80664920385966</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.9230952145464986</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>17.83342091411231</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.03536054261405089</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.9992556045629514</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1.199863797070839</v>
+      </c>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr"/>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="n">
+        <v>6.80845382890728</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.922850542145485</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>17.83814903173707</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.06403350826087298</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>3.948903220766222</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.9992571606462729</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>1.19970570478913</v>
+      </c>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="n">
+        <v>1.007751143403913</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.5501749660009879</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1.055152507143499</v>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
+          <t>PROCESSED-20251113-tett6roof</t>
+        </is>
+      </c>
+      <c r="DC11" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>1.299826689774697</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>1.299826689774697</v>
       </c>
     </row>
   </sheetData>

--- a/waveprocessed/PROCESSED-20251113-tett6roof/meta.xlsx
+++ b/waveprocessed/PROCESSED-20251113-tett6roof/meta.xlsx
@@ -1027,49 +1027,49 @@
         <v>268.57</v>
       </c>
       <c r="P2" t="n">
-        <v>3950</v>
+        <v>5056</v>
       </c>
       <c r="Q2" t="n">
-        <v>13180.76923076923</v>
+        <v>14284</v>
       </c>
       <c r="R2" t="n">
-        <v>14.16499999999999</v>
+        <v>13.995</v>
       </c>
       <c r="S2" t="n">
-        <v>13.39009868255403</v>
+        <v>13.23532396806784</v>
       </c>
       <c r="T2" t="n">
-        <v>13.41242867994689</v>
+        <v>13.24545426723541</v>
       </c>
       <c r="U2" t="n">
-        <v>18.99453828539584</v>
+        <v>18.75317847796562</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2865873607884505</v>
+        <v>0.26272994877728</v>
       </c>
       <c r="W2" t="n">
-        <v>18.99670016057347</v>
+        <v>18.75501879637601</v>
       </c>
       <c r="X2" t="n">
-        <v>1.5385</v>
+        <v>1.538166666666667</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.048927717267306</v>
+        <v>2.04954225440786</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.066572458475788</v>
+        <v>3.065652973812381</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.368190619240342</v>
+        <v>5.369800706548593</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.02902306111509137</v>
+        <v>0.02868334385043801</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8301859775481096</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993056435461511</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -1080,49 +1080,49 @@
         <v>268.99</v>
       </c>
       <c r="AI2" t="n">
-        <v>4000</v>
+        <v>5127</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13230.76923076923</v>
+        <v>14364</v>
       </c>
       <c r="AK2" t="n">
         <v>14.21000000000001</v>
       </c>
       <c r="AL2" t="n">
-        <v>13.91036414153451</v>
+        <v>13.85921893114225</v>
       </c>
       <c r="AM2" t="n">
-        <v>13.94189716118786</v>
+        <v>13.87858922484622</v>
       </c>
       <c r="AN2" t="n">
-        <v>19.74067931459041</v>
+        <v>19.6449006863491</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.3380549458886371</v>
+        <v>0.3379300053565877</v>
       </c>
       <c r="AP2" t="n">
-        <v>19.7435736620283</v>
+        <v>19.64780699378533</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.5385</v>
+        <v>1.539666666666667</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046779967151801</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.066572458475788</v>
+        <v>3.069790308688119</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.368190619240342</v>
+        <v>5.36256351393772</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.02911526286236844</v>
+        <v>0.02908474333322711</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8296873878994435</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.993222267452576</v>
+        <v>1.99380188916743</v>
       </c>
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
@@ -1133,49 +1133,49 @@
         <v>269.77</v>
       </c>
       <c r="BB2" t="n">
-        <v>4500</v>
+        <v>5506</v>
       </c>
       <c r="BC2" t="n">
-        <v>13730.76923076923</v>
+        <v>14745</v>
       </c>
       <c r="BD2" t="n">
-        <v>14.255</v>
+        <v>13.99500000000002</v>
       </c>
       <c r="BE2" t="n">
-        <v>13.45351169007479</v>
+        <v>13.37045069039328</v>
       </c>
       <c r="BF2" t="n">
-        <v>13.47736488995544</v>
+        <v>13.38769826453664</v>
       </c>
       <c r="BG2" t="n">
-        <v>19.08716375662472</v>
+        <v>18.95800831398028</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.3552920517362823</v>
+        <v>0.3596688652075067</v>
       </c>
       <c r="BI2" t="n">
-        <v>19.09047020673496</v>
+        <v>18.96141980247114</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.5385</v>
+        <v>1.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046167216896666</v>
       </c>
       <c r="BL2" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070709595625828</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360958108269264</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.02920746460964544</v>
+        <v>0.02863611020046887</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295766074154407</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993967269886901</v>
       </c>
       <c r="BQ2" t="inlineStr"/>
       <c r="BR2" t="inlineStr"/>
@@ -1186,49 +1186,49 @@
         <v>270.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4500</v>
+        <v>5505</v>
       </c>
       <c r="BV2" t="n">
-        <v>13730.76923076923</v>
+        <v>14744</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.205</v>
+        <v>13.98999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>13.49011914776492</v>
+        <v>13.40817914431311</v>
       </c>
       <c r="BY2" t="n">
-        <v>13.5177041557873</v>
+        <v>13.43347586193522</v>
       </c>
       <c r="BZ2" t="n">
-        <v>19.14681533153997</v>
+        <v>19.02529384030651</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.3169561893703797</v>
+        <v>0.3190213887418112</v>
       </c>
       <c r="CB2" t="n">
-        <v>19.14943859662926</v>
+        <v>19.02796837175424</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.5385</v>
+        <v>1.54</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046167216896666</v>
       </c>
       <c r="CE2" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070709595625828</v>
       </c>
       <c r="CF2" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360958108269264</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.02910501822378208</v>
+        <v>0.02862587936438434</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295766074154407</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993967269886901</v>
       </c>
       <c r="CJ2" t="inlineStr"/>
       <c r="CK2" t="inlineStr"/>
@@ -1262,13 +1262,13 @@
       </c>
       <c r="CX2" t="inlineStr"/>
       <c r="CY2" t="n">
-        <v>1.038854490270362</v>
+        <v>1.047138624228591</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.9671574053122296</v>
+        <v>0.9647333487422809</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.002721033625528</v>
+        <v>1.002821778771223</v>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
@@ -1276,16 +1276,16 @@
         </is>
       </c>
       <c r="DC2" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6501246072163831</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6494912318683699</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6493506493506493</v>
       </c>
     </row>
     <row r="3">
@@ -1347,49 +1347,49 @@
         <v>268.57</v>
       </c>
       <c r="P3" t="n">
-        <v>3950</v>
+        <v>5056</v>
       </c>
       <c r="Q3" t="n">
-        <v>13180.76923076923</v>
+        <v>14288</v>
       </c>
       <c r="R3" t="n">
-        <v>4.849999999999994</v>
+        <v>4.684200000000004</v>
       </c>
       <c r="S3" t="n">
-        <v>4.46473682383476</v>
+        <v>4.411162991033712</v>
       </c>
       <c r="T3" t="n">
-        <v>4.470958810408151</v>
+        <v>4.41293251317488</v>
       </c>
       <c r="U3" t="n">
-        <v>6.330741926478114</v>
+        <v>6.246400070427579</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1389036475183248</v>
+        <v>0.1374393873466214</v>
       </c>
       <c r="W3" t="n">
-        <v>6.332265594790045</v>
+        <v>6.24791192519804</v>
       </c>
       <c r="X3" t="n">
-        <v>1.5385</v>
+        <v>1.538833333333333</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.048927717267306</v>
+        <v>2.048313577898088</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.066572458475788</v>
+        <v>3.067491899178437</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.368190619240342</v>
+        <v>5.36658157409299</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009937299428746422</v>
+        <v>0.009594710461590231</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8299643665751059</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993387999032885</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
@@ -1400,49 +1400,49 @@
         <v>268.99</v>
       </c>
       <c r="AI3" t="n">
-        <v>4000</v>
+        <v>5122</v>
       </c>
       <c r="AJ3" t="n">
-        <v>13230.76923076923</v>
+        <v>14365</v>
       </c>
       <c r="AK3" t="n">
         <v>5.109999999999985</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.764172512009643</v>
+        <v>4.762159607985915</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.780234455321449</v>
+        <v>4.77406971444634</v>
       </c>
       <c r="AN3" t="n">
-        <v>6.769516667500678</v>
+        <v>6.757314979575546</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2870346892296441</v>
+        <v>0.2894832037582157</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.775599222533063</v>
+        <v>6.763512863775316</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.5385</v>
+        <v>1.540666666666667</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.048927717267306</v>
+        <v>2.044942904027034</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.066572458475788</v>
+        <v>3.072548037799163</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.368190619240342</v>
+        <v>5.357750408550831</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0104700206352359</v>
+        <v>0.01044965823957811</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8293550654258437</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994297731154801</v>
       </c>
       <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
@@ -1453,49 +1453,49 @@
         <v>269.77</v>
       </c>
       <c r="BB3" t="n">
-        <v>4500</v>
+        <v>5508</v>
       </c>
       <c r="BC3" t="n">
-        <v>13730.76923076923</v>
+        <v>14750</v>
       </c>
       <c r="BD3" t="n">
         <v>4.685000000000031</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.529616432010443</v>
+        <v>4.522943164648665</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.534792249990878</v>
+        <v>4.525220864161554</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.420427419951952</v>
+        <v>6.407786490265729</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1366299096744683</v>
+        <v>0.1348602118527817</v>
       </c>
       <c r="BI3" t="n">
-        <v>6.421881031838609</v>
+        <v>6.409205487544689</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.5385</v>
+        <v>1.5405</v>
       </c>
       <c r="BK3" t="n">
-        <v>2.048927717267306</v>
+        <v>2.045248833911213</v>
       </c>
       <c r="BL3" t="n">
-        <v>3.066572458475788</v>
+        <v>3.072088443714691</v>
       </c>
       <c r="BM3" t="n">
-        <v>5.368190619240342</v>
+        <v>5.358551944847379</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.009599226355397393</v>
+        <v>0.009581990786874099</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8294104485427312</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994215153336379</v>
       </c>
       <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="inlineStr"/>
@@ -1506,49 +1506,49 @@
         <v>270.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>4500</v>
+        <v>5506</v>
       </c>
       <c r="BV3" t="n">
-        <v>13730.76923076923</v>
+        <v>14745</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.889999999999986</v>
+        <v>4.765000000000015</v>
       </c>
       <c r="BX3" t="n">
-        <v>4.55845385710621</v>
+        <v>4.551743882987567</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.567881665772925</v>
+        <v>4.556963397855079</v>
       </c>
       <c r="BZ3" t="n">
-        <v>6.464856738559091</v>
+        <v>6.449707859168766</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1209979828152048</v>
+        <v>0.1202189666462673</v>
       </c>
       <c r="CB3" t="n">
-        <v>6.465988954671841</v>
+        <v>6.450828169201597</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.5385</v>
+        <v>1.54</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.048927717267306</v>
+        <v>2.046167216896666</v>
       </c>
       <c r="CE3" t="n">
-        <v>3.066572458475788</v>
+        <v>3.070709595625828</v>
       </c>
       <c r="CF3" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360958108269264</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.0100192565374371</v>
+        <v>0.009749986788512643</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295766074154407</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.993222267452576</v>
+        <v>1.993967269886901</v>
       </c>
       <c r="CJ3" t="inlineStr"/>
       <c r="CK3" t="inlineStr"/>
@@ -1582,13 +1582,13 @@
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.067066817147287</v>
+        <v>1.079570085636294</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.9507666694671687</v>
+        <v>0.9497672352400588</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.00636641656719</v>
+        <v>1.00636769406346</v>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
@@ -1596,16 +1596,16 @@
         </is>
       </c>
       <c r="DC3" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6498429546193003</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6490696668109044</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6491398896462188</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6493506493506493</v>
       </c>
     </row>
     <row r="4">
@@ -1667,49 +1667,49 @@
         <v>268.57</v>
       </c>
       <c r="P4" t="n">
-        <v>4700</v>
+        <v>4769</v>
       </c>
       <c r="Q4" t="n">
-        <v>9315.384615384615</v>
+        <v>9383</v>
       </c>
       <c r="R4" t="n">
-        <v>16.782</v>
+        <v>16.7822</v>
       </c>
       <c r="S4" t="n">
-        <v>15.47118888520432</v>
+        <v>15.50245816513323</v>
       </c>
       <c r="T4" t="n">
-        <v>15.63633054529925</v>
+        <v>15.62854242029992</v>
       </c>
       <c r="U4" t="n">
-        <v>22.1604006437392</v>
+        <v>22.14580515697203</v>
       </c>
       <c r="V4" t="n">
-        <v>1.790068380971786</v>
+        <v>1.793925904474765</v>
       </c>
       <c r="W4" t="n">
-        <v>22.23258198004882</v>
+        <v>22.21834503740805</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7691666666666667</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.80664920385966</v>
+        <v>6.809582094531432</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9226976369409542</v>
       </c>
       <c r="AA4" t="n">
-        <v>17.83342091411231</v>
+        <v>17.84110508767235</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1142291869391728</v>
+        <v>0.1142797686268454</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992581318692667</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.199863797070839</v>
+        <v>1.199606895264513</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1720,49 +1720,49 @@
         <v>268.99</v>
       </c>
       <c r="AI4" t="n">
-        <v>4800</v>
+        <v>4888</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9415.384615384615</v>
+        <v>9506</v>
       </c>
       <c r="AK4" t="n">
-        <v>16.95662500000003</v>
+        <v>16.95595000000002</v>
       </c>
       <c r="AL4" t="n">
-        <v>15.60483756739707</v>
+        <v>15.63153120870922</v>
       </c>
       <c r="AM4" t="n">
-        <v>15.63571286140404</v>
+        <v>15.64485030046456</v>
       </c>
       <c r="AN4" t="n">
-        <v>22.16823773450984</v>
+        <v>22.17540828546525</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.796019688892619</v>
+        <v>1.777971456305254</v>
       </c>
       <c r="AP4" t="n">
-        <v>22.24087343106461</v>
+        <v>22.24657086219171</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7698333333333333</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.80664920385966</v>
+        <v>6.797862219213146</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.924288416646795</v>
       </c>
       <c r="AT4" t="n">
-        <v>17.83342091411231</v>
+        <v>17.81039901433844</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.115417798056397</v>
+        <v>0.1152642118958672</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992479810793535</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200634444659184</v>
       </c>
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
@@ -1773,49 +1773,49 @@
         <v>269.77</v>
       </c>
       <c r="BB4" t="n">
-        <v>6500</v>
+        <v>6487</v>
       </c>
       <c r="BC4" t="n">
-        <v>11115.38461538462</v>
+        <v>11097</v>
       </c>
       <c r="BD4" t="n">
         <v>11.72000000000003</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.16099133249193</v>
+        <v>10.17110813846172</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.982052026791816</v>
+        <v>9.974997703430597</v>
       </c>
       <c r="BG4" t="n">
-        <v>14.1481755937165</v>
+        <v>14.13739199002569</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.9819887676947914</v>
+        <v>0.9802460986715852</v>
       </c>
       <c r="BI4" t="n">
-        <v>14.18221331705718</v>
+        <v>14.17133496511896</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7685000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.80664920385966</v>
+        <v>6.821333179279163</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9211081092279317</v>
       </c>
       <c r="BM4" t="n">
-        <v>17.83342091411231</v>
+        <v>17.87189292971141</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0797739286692354</v>
+        <v>0.07994602486115197</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992681721785561</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.199863797070839</v>
+        <v>1.198579192228929</v>
       </c>
       <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="inlineStr"/>
@@ -1826,49 +1826,49 @@
         <v>270.2</v>
       </c>
       <c r="BU4" t="n">
-        <v>6500</v>
+        <v>6486</v>
       </c>
       <c r="BV4" t="n">
-        <v>11115.38461538462</v>
+        <v>11100</v>
       </c>
       <c r="BW4" t="n">
         <v>11.97500000000002</v>
       </c>
       <c r="BX4" t="n">
-        <v>10.57923493858625</v>
+        <v>10.58218689573083</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.42531591863569</v>
+        <v>10.42003156354987</v>
       </c>
       <c r="BZ4" t="n">
-        <v>14.78683263613222</v>
+        <v>14.77817280099178</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.538181810275313</v>
+        <v>1.543667421847182</v>
       </c>
       <c r="CB4" t="n">
-        <v>14.86662109191079</v>
+        <v>14.85857666283165</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7691666666666667</v>
       </c>
       <c r="CD4" t="n">
-        <v>6.80664920385966</v>
+        <v>6.809582094531432</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9226976369409542</v>
       </c>
       <c r="CF4" t="n">
-        <v>17.83342091411231</v>
+        <v>17.84110508767235</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.08150962421621959</v>
+        <v>0.08154474558201406</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992581318692667</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.199863797070839</v>
+        <v>1.199606895264513</v>
       </c>
       <c r="CJ4" t="inlineStr"/>
       <c r="CK4" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.1154483984065951</v>
+        <v>0.1154438027002605</v>
       </c>
       <c r="CQ4" t="n">
         <v>3.948903220766222</v>
@@ -1902,13 +1902,13 @@
       </c>
       <c r="CX4" t="inlineStr"/>
       <c r="CY4" t="n">
-        <v>1.008638552808347</v>
+        <v>1.008325972707108</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.6511436782732762</v>
+        <v>0.6506789387846289</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.041161693028602</v>
+        <v>1.040416319605789</v>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
@@ -1916,16 +1916,16 @@
         </is>
       </c>
       <c r="DC4" t="n">
-        <v>1.299826689774697</v>
+        <v>1.300108342361864</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29898246373674</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.299826689774697</v>
+        <v>1.301236174365647</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.299826689774697</v>
+        <v>1.300108342361864</v>
       </c>
     </row>
     <row r="5">
@@ -1987,49 +1987,49 @@
         <v>268.57</v>
       </c>
       <c r="P5" t="n">
-        <v>4700</v>
+        <v>4772</v>
       </c>
       <c r="Q5" t="n">
-        <v>9315.384615384615</v>
+        <v>9391</v>
       </c>
       <c r="R5" t="n">
         <v>8.414999999999992</v>
       </c>
       <c r="S5" t="n">
-        <v>7.823183711811956</v>
+        <v>7.823003292339097</v>
       </c>
       <c r="T5" t="n">
-        <v>7.732526771658283</v>
+        <v>7.738531178615712</v>
       </c>
       <c r="U5" t="n">
-        <v>10.96242803326361</v>
+        <v>10.96806825845865</v>
       </c>
       <c r="V5" t="n">
-        <v>1.021131359922834</v>
+        <v>1.022672140608143</v>
       </c>
       <c r="W5" t="n">
-        <v>11.00988363420349</v>
+        <v>11.01564249734822</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.77</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.80664920385966</v>
+        <v>6.794937114744855</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9246863070366348</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.83342091411231</v>
+        <v>17.80273524063152</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05727795305047898</v>
+        <v>0.0571793958205779</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992454260183794</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200891307839786</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -2040,49 +2040,49 @@
         <v>268.99</v>
       </c>
       <c r="AI5" t="n">
-        <v>4800</v>
+        <v>4712</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9415.384615384615</v>
+        <v>9324</v>
       </c>
       <c r="AK5" t="n">
-        <v>8.539999999999992</v>
+        <v>8.585000000000008</v>
       </c>
       <c r="AL5" t="n">
-        <v>7.512481246199147</v>
+        <v>7.538819418326574</v>
       </c>
       <c r="AM5" t="n">
-        <v>7.623165263513712</v>
+        <v>7.640936434146474</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.81554678132595</v>
+        <v>10.84179847975882</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.334633275989068</v>
+        <v>1.355728788648373</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.8975822162729</v>
+        <v>10.92623424717183</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7688333333333335</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.80664920385966</v>
+        <v>6.815453729254355</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9219027164999912</v>
       </c>
       <c r="AT5" t="n">
-        <v>17.83342091411231</v>
+        <v>17.85648877064641</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.05812878420096144</v>
+        <v>0.05851067026564869</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992631657802564</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.199863797070839</v>
+        <v>1.199093062865803</v>
       </c>
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
@@ -2093,49 +2093,49 @@
         <v>269.77</v>
       </c>
       <c r="BB5" t="n">
-        <v>6500</v>
+        <v>6497</v>
       </c>
       <c r="BC5" t="n">
-        <v>11115.38461538462</v>
+        <v>11115</v>
       </c>
       <c r="BD5" t="n">
         <v>4.724999999999994</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.323150470516596</v>
+        <v>4.316255742866535</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.350858132791348</v>
+        <v>4.350599704682407</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.159907147638667</v>
+        <v>6.159443024681111</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.3547009822265755</v>
+        <v>0.354709078092185</v>
       </c>
       <c r="BI5" t="n">
-        <v>6.170110927229951</v>
+        <v>6.169648037317347</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7698333333333333</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.80664920385966</v>
+        <v>6.797862219213146</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.924288416646795</v>
       </c>
       <c r="BM5" t="n">
-        <v>17.83342091411231</v>
+        <v>17.81039901433844</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.03216141748823686</v>
+        <v>0.03211989898578207</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992479810793535</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200634444659184</v>
       </c>
       <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="inlineStr"/>
@@ -2146,49 +2146,49 @@
         <v>270.2</v>
       </c>
       <c r="BU5" t="n">
-        <v>6500</v>
+        <v>6496</v>
       </c>
       <c r="BV5" t="n">
-        <v>11115.38461538462</v>
+        <v>11117</v>
       </c>
       <c r="BW5" t="n">
         <v>4.940000000000026</v>
       </c>
       <c r="BX5" t="n">
-        <v>4.516689190015959</v>
+        <v>4.497048566648595</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.550798463013243</v>
+        <v>4.550462185463913</v>
       </c>
       <c r="BZ5" t="n">
-        <v>6.443504927646345</v>
+        <v>6.442934300256664</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.3992269192931915</v>
+        <v>0.3993105001606747</v>
       </c>
       <c r="CB5" t="n">
-        <v>6.455860739335312</v>
+        <v>6.455296373750968</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7703333333333333</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.80664920385966</v>
+        <v>6.789092731771489</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9254823222218832</v>
       </c>
       <c r="CF5" t="n">
-        <v>17.83342091411231</v>
+        <v>17.7874229572413</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0336248470670669</v>
+        <v>0.03353811809495133</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992402949658459</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.199863797070839</v>
+        <v>1.20140500504788</v>
       </c>
       <c r="CJ5" t="inlineStr"/>
       <c r="CK5" t="inlineStr"/>
@@ -2203,7 +2203,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.05814419569886811</v>
+        <v>0.05845057612116905</v>
       </c>
       <c r="CQ5" t="n">
         <v>3.948903220766222</v>
@@ -2222,13 +2222,13 @@
       </c>
       <c r="CX5" t="inlineStr"/>
       <c r="CY5" t="n">
-        <v>0.9602843960900866</v>
+        <v>0.96367330251659</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.5754623976870283</v>
+        <v>0.5725373567609123</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.044767981318086</v>
+        <v>1.041886494812282</v>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
@@ -2236,16 +2236,16 @@
         </is>
       </c>
       <c r="DC5" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298701298701299</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.299826689774697</v>
+        <v>1.300672013873835</v>
       </c>
       <c r="DE5" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29898246373674</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.299826689774697</v>
+        <v>1.298139333621809</v>
       </c>
     </row>
     <row r="6">
@@ -2307,49 +2307,49 @@
         <v>268.57</v>
       </c>
       <c r="P6" t="n">
-        <v>3950</v>
+        <v>5056</v>
       </c>
       <c r="Q6" t="n">
-        <v>13180.76923076923</v>
+        <v>14285</v>
       </c>
       <c r="R6" t="n">
-        <v>9.490000000000009</v>
+        <v>9.274999999999977</v>
       </c>
       <c r="S6" t="n">
-        <v>8.888370382137218</v>
+        <v>8.777052467741445</v>
       </c>
       <c r="T6" t="n">
-        <v>8.902653780747572</v>
+        <v>8.781902256982624</v>
       </c>
       <c r="U6" t="n">
-        <v>12.60745131773329</v>
+        <v>12.43350251851313</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2615054453026831</v>
+        <v>0.2324289811157213</v>
       </c>
       <c r="W6" t="n">
-        <v>12.61016311658726</v>
+        <v>12.43567481518936</v>
       </c>
       <c r="X6" t="n">
-        <v>1.5385</v>
+        <v>1.538333333333333</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.048927717267306</v>
+        <v>2.049234936091632</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.066572458475788</v>
+        <v>3.066112721639952</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.368190619240342</v>
+        <v>5.368995532560076</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01944432403686675</v>
+        <v>0.01900665403224984</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8301305724820542</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.993222267452576</v>
+        <v>1.99313936401297</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -2360,49 +2360,49 @@
         <v>268.99</v>
       </c>
       <c r="AI6" t="n">
-        <v>4000</v>
+        <v>5127</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13230.76923076923</v>
+        <v>14367</v>
       </c>
       <c r="AK6" t="n">
-        <v>9.659999999999997</v>
+        <v>9.615000000000009</v>
       </c>
       <c r="AL6" t="n">
-        <v>9.320232764156783</v>
+        <v>9.296803540118047</v>
       </c>
       <c r="AM6" t="n">
-        <v>9.349100963432806</v>
+        <v>9.317769494964724</v>
       </c>
       <c r="AN6" t="n">
-        <v>13.23596131692082</v>
+        <v>13.18830603861544</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.3187290227860898</v>
+        <v>0.3189296628970761</v>
       </c>
       <c r="AP6" t="n">
-        <v>13.23979834336575</v>
+        <v>13.1921617750108</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.5385</v>
+        <v>1.540166666666667</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.048927717267306</v>
+        <v>2.045860990297312</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.066572458475788</v>
+        <v>3.071169222629584</v>
       </c>
       <c r="AT6" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360155794578957</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.01979264174880217</v>
+        <v>0.01967095342170867</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295212195408118</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994049922711558</v>
       </c>
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
@@ -2413,49 +2413,49 @@
         <v>269.77</v>
       </c>
       <c r="BB6" t="n">
-        <v>4500</v>
+        <v>5508</v>
       </c>
       <c r="BC6" t="n">
-        <v>13730.76923076923</v>
+        <v>14748</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.445000000000022</v>
+        <v>9.275000000000006</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.998638508131421</v>
+        <v>8.952995841567029</v>
       </c>
       <c r="BF6" t="n">
-        <v>9.020517659632313</v>
+        <v>8.964047679962674</v>
       </c>
       <c r="BG6" t="n">
-        <v>12.76893679099696</v>
+        <v>12.69022566068974</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.2479633341126553</v>
+        <v>0.2456517561541078</v>
       </c>
       <c r="BI6" t="n">
-        <v>12.77134419658088</v>
+        <v>12.69260304683519</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.5385</v>
+        <v>1.540166666666667</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.048927717267306</v>
+        <v>2.045860990297312</v>
       </c>
       <c r="BL6" t="n">
-        <v>3.066572458475788</v>
+        <v>3.071169222629584</v>
       </c>
       <c r="BM6" t="n">
-        <v>5.368190619240342</v>
+        <v>5.360155794578957</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.01935212228958975</v>
+        <v>0.01897536068500758</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.8295212195408118</v>
       </c>
       <c r="BP6" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994049922711558</v>
       </c>
       <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="inlineStr"/>
@@ -2466,49 +2466,49 @@
         <v>270.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4500</v>
+        <v>5505</v>
       </c>
       <c r="BV6" t="n">
-        <v>13730.76923076923</v>
+        <v>14746</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.615000000000009</v>
+        <v>9.399999999999977</v>
       </c>
       <c r="BX6" t="n">
-        <v>9.03487340262007</v>
+        <v>8.99005257990731</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.056478451834783</v>
+        <v>9.001735955204566</v>
       </c>
       <c r="BZ6" t="n">
-        <v>12.82214090567734</v>
+        <v>12.74408936091035</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.237999349226677</v>
+        <v>0.2317602133697638</v>
       </c>
       <c r="CB6" t="n">
-        <v>12.82434953887629</v>
+        <v>12.74619654780867</v>
       </c>
       <c r="CC6" t="n">
-        <v>1.5385</v>
+        <v>1.540333333333334</v>
       </c>
       <c r="CD6" t="n">
-        <v>2.048927717267306</v>
+        <v>2.045554862651738</v>
       </c>
       <c r="CE6" t="n">
-        <v>3.066572458475788</v>
+        <v>3.071628838658687</v>
       </c>
       <c r="CF6" t="n">
-        <v>5.368190619240342</v>
+        <v>5.359353740147553</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01970044000152517</v>
+        <v>0.01922821570892629</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.8300751689623258</v>
+        <v>0.829465833248814</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.993222267452576</v>
+        <v>1.994132550525007</v>
       </c>
       <c r="CJ6" t="inlineStr"/>
       <c r="CK6" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
         <v>5.368376345338421</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.01979332652517905</v>
+        <v>0.01970112158794998</v>
       </c>
       <c r="CQ6" t="n">
         <v>1.18841919095278</v>
@@ -2542,13 +2542,13 @@
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
-        <v>1.048587352175093</v>
+        <v>1.059217040605244</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.9654950402888938</v>
+        <v>0.9630187195989028</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.004026708535509</v>
+        <v>1.004139032229663</v>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
@@ -2556,16 +2556,16 @@
         </is>
       </c>
       <c r="DC6" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6500541711809318</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6492803809111568</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6492803809111568</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.6499837504062399</v>
+        <v>0.6492101276779917</v>
       </c>
     </row>
     <row r="7">
@@ -2625,49 +2625,49 @@
         <v>268.57</v>
       </c>
       <c r="P7" t="n">
-        <v>4700</v>
+        <v>4697</v>
       </c>
       <c r="Q7" t="n">
-        <v>9315.384615384615</v>
+        <v>9317</v>
       </c>
       <c r="R7" t="n">
         <v>0.04499999999998749</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001121612569711128</v>
+        <v>0.001090208173098832</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002756446477178402</v>
+        <v>0.002756406896503666</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005718307937832363</v>
+        <v>0.005712762783380565</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01570310632939529</v>
+        <v>0.01570421996978535</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01671186985541029</v>
+        <v>0.01671101982162019</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9232</v>
+        <v>0.9242000000000002</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.761201086064131</v>
+        <v>4.751339878813758</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.319663923788107</v>
+        <v>1.32240283108273</v>
       </c>
       <c r="AA7" t="n">
-        <v>12.47434684548802</v>
+        <v>12.44851048249205</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0002142540488728263</v>
+        <v>0.0002138102945465597</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.992044024522438</v>
+        <v>0.9919528618836188</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.429445324727152</v>
+        <v>1.430862184681594</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -2678,49 +2678,49 @@
         <v>268.99</v>
       </c>
       <c r="AI7" t="n">
-        <v>4800</v>
+        <v>4803</v>
       </c>
       <c r="AJ7" t="n">
-        <v>9415.384615384615</v>
+        <v>9385</v>
       </c>
       <c r="AK7" t="n">
         <v>0.2200000000000273</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.01383000732085631</v>
+        <v>0.01247892547452638</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.02857499214500419</v>
+        <v>0.02854560553662995</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08837479428376437</v>
+        <v>0.08824178685917168</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1367816149230967</v>
+        <v>0.1368010266344127</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.1628475190037232</v>
+        <v>0.1627916884743467</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.025777777777778</v>
+        <v>1.018444444444444</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.908915257338599</v>
+        <v>3.960471058416543</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.60739870105486</v>
+        <v>1.586474238670917</v>
       </c>
       <c r="AT7" t="n">
-        <v>10.24135797422713</v>
+        <v>10.37643417305134</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0008599613566145985</v>
+        <v>0.0008713036328517476</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.9787600468623101</v>
+        <v>0.9799807170410417</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.567004799555214</v>
+        <v>1.557742542880019</v>
       </c>
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
@@ -2731,49 +2731,49 @@
         <v>269.77</v>
       </c>
       <c r="BB7" t="n">
-        <v>6500</v>
+        <v>6473</v>
       </c>
       <c r="BC7" t="n">
-        <v>11115.38461538462</v>
+        <v>11073</v>
       </c>
       <c r="BD7" t="n">
         <v>0.04499999999998749</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.005744110784569817</v>
+        <v>0.00609717604840619</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.01174336482107343</v>
+        <v>0.0118918229159119</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.02343183180151267</v>
+        <v>0.02358446724261807</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.04575235388411374</v>
+        <v>0.0458057331656608</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.05140358574566133</v>
+        <v>0.05152079469458756</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8792380952380952</v>
+        <v>0.8763809523809524</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.231619913490253</v>
+        <v>5.264865413540321</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.20100187151933</v>
+        <v>1.193418029456237</v>
       </c>
       <c r="BM7" t="n">
-        <v>13.70684417334446</v>
+        <v>13.79394738347564</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0002354228961069959</v>
+        <v>0.0002369189436092486</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.9953822304573618</v>
+        <v>0.9955565354516305</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.365957501186412</v>
+        <v>1.361757151629047</v>
       </c>
       <c r="BQ7" t="inlineStr"/>
       <c r="BR7" t="inlineStr"/>
@@ -2784,49 +2784,49 @@
         <v>270.2</v>
       </c>
       <c r="BU7" t="n">
-        <v>6500</v>
+        <v>6365</v>
       </c>
       <c r="BV7" t="n">
-        <v>11115.38461538462</v>
+        <v>10917</v>
       </c>
       <c r="BW7" t="n">
         <v>0.08500000000000796</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.002129431812910728</v>
+        <v>0.002853171012523622</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.004436194125615608</v>
+        <v>0.003997257157847551</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.009149683148973494</v>
+        <v>0.008384627958057323</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.01827654582425401</v>
+        <v>0.01722708092691218</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.02043890478946135</v>
+        <v>0.01915918326175253</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.6838518518518518</v>
+        <v>0.7004615384615385</v>
       </c>
       <c r="CD7" t="n">
-        <v>8.609044975343432</v>
+        <v>8.206051993996168</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.7298353447072029</v>
+        <v>0.7656770042130592</v>
       </c>
       <c r="CF7" t="n">
-        <v>22.55569783539979</v>
+        <v>21.49985622426996</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0007317688229042602</v>
+        <v>0.0006975144194897396</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.9999079695453716</v>
+        <v>0.9998531276287881</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.067241892715255</v>
+        <v>1.093103564108255</v>
       </c>
       <c r="CJ7" t="inlineStr"/>
       <c r="CK7" t="inlineStr"/>
@@ -2860,13 +2860,13 @@
       </c>
       <c r="CX7" t="inlineStr"/>
       <c r="CY7" t="n">
-        <v>12.33046748434553</v>
+        <v>11.44636940214455</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.4153367855349886</v>
+        <v>0.4885978412846961</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.3707156586587672</v>
+        <v>0.4679495868041147</v>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
@@ -2874,16 +2874,16 @@
         </is>
       </c>
       <c r="DC7" t="n">
-        <v>1.083188908145581</v>
+        <v>1.082016879463319</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.9748700173310225</v>
+        <v>0.981889591970325</v>
       </c>
       <c r="DE7" t="n">
-        <v>1.13734835355286</v>
+        <v>1.141056292110411</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.462305025996534</v>
+        <v>1.427630133977597</v>
       </c>
     </row>
     <row r="8">
@@ -2945,49 +2945,49 @@
         <v>268.57</v>
       </c>
       <c r="P8" t="n">
-        <v>4700</v>
+        <v>4752</v>
       </c>
       <c r="Q8" t="n">
-        <v>9315.384615384615</v>
+        <v>9369</v>
       </c>
       <c r="R8" t="n">
-        <v>26.14162499999999</v>
+        <v>26.011175</v>
       </c>
       <c r="S8" t="n">
-        <v>22.75401383226536</v>
+        <v>22.70230483946847</v>
       </c>
       <c r="T8" t="n">
-        <v>22.73657371653815</v>
+        <v>22.70022542526193</v>
       </c>
       <c r="U8" t="n">
-        <v>32.35148773854499</v>
+        <v>32.29380065571434</v>
       </c>
       <c r="V8" t="n">
-        <v>4.735122399204909</v>
+        <v>4.756932353038613</v>
       </c>
       <c r="W8" t="n">
-        <v>32.69617933387138</v>
+        <v>32.64227268745853</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="AA8" t="n">
-        <v>17.83342091411231</v>
+        <v>17.81806788167299</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1779368709938478</v>
+        <v>0.1768965197832349</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
@@ -2998,28 +2998,28 @@
         <v>268.99</v>
       </c>
       <c r="AI8" t="n">
-        <v>4800</v>
+        <v>4873</v>
       </c>
       <c r="AJ8" t="n">
-        <v>9415.384615384615</v>
+        <v>9488</v>
       </c>
       <c r="AK8" t="n">
         <v>24.59662500000002</v>
       </c>
       <c r="AL8" t="n">
-        <v>22.52843153723217</v>
+        <v>22.57750218168116</v>
       </c>
       <c r="AM8" t="n">
-        <v>22.35088360837119</v>
+        <v>22.36922676548797</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.66707841846137</v>
+        <v>31.68858093236593</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.093391488865637</v>
+        <v>2.04632761530616</v>
       </c>
       <c r="AP8" t="n">
-        <v>31.73619610927933</v>
+        <v>31.75458420789462</v>
       </c>
       <c r="AQ8" t="n">
         <v>0.7693333333333332</v>
@@ -3051,49 +3051,49 @@
         <v>269.77</v>
       </c>
       <c r="BB8" t="n">
-        <v>6500</v>
+        <v>6459</v>
       </c>
       <c r="BC8" t="n">
-        <v>11115.38461538462</v>
+        <v>11077</v>
       </c>
       <c r="BD8" t="n">
         <v>18.02999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>15.9102117780071</v>
+        <v>15.92887330045943</v>
       </c>
       <c r="BF8" t="n">
-        <v>15.97960807881907</v>
+        <v>15.97234603657705</v>
       </c>
       <c r="BG8" t="n">
-        <v>22.65377377393175</v>
+        <v>22.64555104545629</v>
       </c>
       <c r="BH8" t="n">
-        <v>1.885899445029984</v>
+        <v>1.855887638532504</v>
       </c>
       <c r="BI8" t="n">
-        <v>22.73213766712762</v>
+        <v>22.72147224717678</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.809582094531432</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="BM8" t="n">
-        <v>17.84110508767235</v>
+        <v>17.81806788167299</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.1227767651644016</v>
+        <v>0.1226182304986884</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="BP8" t="n">
-        <v>1.199606895264513</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="BQ8" t="inlineStr"/>
       <c r="BR8" t="inlineStr"/>
@@ -3104,49 +3104,49 @@
         <v>270.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>6500</v>
+        <v>6460</v>
       </c>
       <c r="BV8" t="n">
-        <v>11115.38461538462</v>
+        <v>11080</v>
       </c>
       <c r="BW8" t="n">
         <v>18.37500000000001</v>
       </c>
       <c r="BX8" t="n">
-        <v>16.15787893864201</v>
+        <v>16.16816897904443</v>
       </c>
       <c r="BY8" t="n">
-        <v>16.27760005290235</v>
+        <v>16.26743832633996</v>
       </c>
       <c r="BZ8" t="n">
-        <v>23.14735346006549</v>
+        <v>23.13957478035838</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.892179268298839</v>
+        <v>3.869433749906555</v>
       </c>
       <c r="CB8" t="n">
-        <v>23.47230350139886</v>
+        <v>23.4608703709115</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.7691666666666667</v>
+        <v>0.77</v>
       </c>
       <c r="CD8" t="n">
-        <v>6.809582094531432</v>
+        <v>6.794937114744855</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.9226976369409542</v>
+        <v>0.9246863070366348</v>
       </c>
       <c r="CF8" t="n">
-        <v>17.84110508767235</v>
+        <v>17.80273524063152</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.1251260709870152</v>
+        <v>0.1248569694834368</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.9992581318692667</v>
+        <v>0.9992454260183794</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.199606895264513</v>
+        <v>1.200891307839786</v>
       </c>
       <c r="CJ8" t="inlineStr"/>
       <c r="CK8" t="inlineStr"/>
@@ -3180,13 +3180,13 @@
       </c>
       <c r="CX8" t="inlineStr"/>
       <c r="CY8" t="n">
-        <v>0.990086043864783</v>
+        <v>0.9945026437328803</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.706228116756051</v>
+        <v>0.70551973253196</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.015566553361487</v>
+        <v>1.015022762380695</v>
       </c>
       <c r="DB8" t="inlineStr">
         <is>
@@ -3194,16 +3194,16 @@
         </is>
       </c>
       <c r="DC8" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
       <c r="DD8" t="n">
         <v>1.299826689774697</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.300108342361864</v>
+        <v>1.29926375054136</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.300108342361864</v>
+        <v>1.298701298701299</v>
       </c>
     </row>
     <row r="9">
@@ -3265,49 +3265,49 @@
         <v>268.57</v>
       </c>
       <c r="P9" t="n">
-        <v>4700</v>
+        <v>4763</v>
       </c>
       <c r="Q9" t="n">
-        <v>9315.384615384615</v>
+        <v>9380</v>
       </c>
       <c r="R9" t="n">
         <v>8.585000000000008</v>
       </c>
       <c r="S9" t="n">
-        <v>7.529046565807</v>
+        <v>7.552480412715393</v>
       </c>
       <c r="T9" t="n">
-        <v>7.545058653798318</v>
+        <v>7.554820013041225</v>
       </c>
       <c r="U9" t="n">
-        <v>10.69182250769127</v>
+        <v>10.7011126983662</v>
       </c>
       <c r="V9" t="n">
-        <v>1.329074950945369</v>
+        <v>1.328246698707814</v>
       </c>
       <c r="W9" t="n">
-        <v>10.7741128990374</v>
+        <v>10.78323014109235</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="AA9" t="n">
-        <v>17.83342091411231</v>
+        <v>17.81806788167299</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05843508341513523</v>
+        <v>0.05838477586418424</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
@@ -3318,49 +3318,49 @@
         <v>268.99</v>
       </c>
       <c r="AI9" t="n">
-        <v>4800</v>
+        <v>4882</v>
       </c>
       <c r="AJ9" t="n">
-        <v>9415.384615384615</v>
+        <v>9504</v>
       </c>
       <c r="AK9" t="n">
         <v>9.274999999999977</v>
       </c>
       <c r="AL9" t="n">
-        <v>7.695264194023932</v>
+        <v>7.671862168889388</v>
       </c>
       <c r="AM9" t="n">
-        <v>7.698276320933147</v>
+        <v>7.703047189755197</v>
       </c>
       <c r="AN9" t="n">
-        <v>10.92079591841597</v>
+        <v>10.92960053799134</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.587495671408587</v>
+        <v>1.612677356434519</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.03557547201015</v>
+        <v>11.04793628584168</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7705000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.80664920385966</v>
+        <v>6.786173450053408</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9258804469741541</v>
       </c>
       <c r="AT9" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77977443913993</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0631316713657982</v>
+        <v>0.06294175874924521</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992377189472729</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201661839031998</v>
       </c>
       <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
@@ -3371,49 +3371,49 @@
         <v>269.77</v>
       </c>
       <c r="BB9" t="n">
-        <v>6500</v>
+        <v>6479</v>
       </c>
       <c r="BC9" t="n">
-        <v>11115.38461538462</v>
+        <v>11107</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.748125000000005</v>
+        <v>4.746499999999997</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.298652906865373</v>
+        <v>4.27936050681619</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.342452515563213</v>
+        <v>4.341142366644808</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.149376937053908</v>
+        <v>6.147639631955067</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.411396388871564</v>
+        <v>0.4111172141590534</v>
       </c>
       <c r="BI9" t="n">
-        <v>6.163122885578955</v>
+        <v>6.161370822159832</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7715000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.80664920385966</v>
+        <v>6.768698395574119</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9282708343583461</v>
       </c>
       <c r="BM9" t="n">
-        <v>17.83342091411231</v>
+        <v>17.73398979640419</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.03231882125107619</v>
+        <v>0.03212762693459253</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992221150908543</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.199863797070839</v>
+        <v>1.203202636887033</v>
       </c>
       <c r="BQ9" t="inlineStr"/>
       <c r="BR9" t="inlineStr"/>
@@ -3424,49 +3424,49 @@
         <v>270.2</v>
       </c>
       <c r="BU9" t="n">
-        <v>6500</v>
+        <v>6480</v>
       </c>
       <c r="BV9" t="n">
-        <v>11115.38461538462</v>
+        <v>11105</v>
       </c>
       <c r="BW9" t="n">
         <v>5.164999999999992</v>
       </c>
       <c r="BX9" t="n">
-        <v>4.473551514851751</v>
+        <v>4.448704766523634</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.455187438226599</v>
+        <v>4.455055137392394</v>
       </c>
       <c r="BZ9" t="n">
-        <v>6.311389941111753</v>
+        <v>6.311041730287092</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.5629158935460172</v>
+        <v>0.5626043134637903</v>
       </c>
       <c r="CB9" t="n">
-        <v>6.336443583902039</v>
+        <v>6.336069075929741</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7710000000000001</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.80664920385966</v>
+        <v>6.777427224732707</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9270752896099725</v>
       </c>
       <c r="CF9" t="n">
-        <v>17.83342091411231</v>
+        <v>17.75685932879969</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.03515634313793509</v>
+        <v>0.03500541161574438</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992299487600118</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202432282243803</v>
       </c>
       <c r="CJ9" t="inlineStr"/>
       <c r="CK9" t="inlineStr"/>
@@ -3500,13 +3500,13 @@
       </c>
       <c r="CX9" t="inlineStr"/>
       <c r="CY9" t="n">
-        <v>1.022076849540525</v>
+        <v>1.015806960051562</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.558610178738719</v>
+        <v>0.5577994511123613</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.04068684115134</v>
+        <v>1.03957232849107</v>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
@@ -3514,16 +3514,16 @@
         </is>
       </c>
       <c r="DC9" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297858533419857</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.299826689774697</v>
+        <v>1.296176279974076</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297016861219196</v>
       </c>
     </row>
     <row r="10">
@@ -3585,49 +3585,49 @@
         <v>268.57</v>
       </c>
       <c r="P10" t="n">
-        <v>4700</v>
+        <v>4763</v>
       </c>
       <c r="Q10" t="n">
-        <v>9315.384615384615</v>
+        <v>9385</v>
       </c>
       <c r="R10" t="n">
         <v>8.844999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>7.495042445971214</v>
+        <v>7.505388286094539</v>
       </c>
       <c r="T10" t="n">
-        <v>7.542812715994216</v>
+        <v>7.536404482938186</v>
       </c>
       <c r="U10" t="n">
-        <v>10.69454968049252</v>
+        <v>10.68369149639186</v>
       </c>
       <c r="V10" t="n">
-        <v>1.342666462164123</v>
+        <v>1.359325651957543</v>
       </c>
       <c r="W10" t="n">
-        <v>10.77850388955457</v>
+        <v>10.76982034289084</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7705000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.80664920385966</v>
+        <v>6.786173450053408</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9258804469741541</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77977443913993</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.06020481220813868</v>
+        <v>0.06002370416572238</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992377189472729</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201661839031998</v>
       </c>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
@@ -3638,49 +3638,49 @@
         <v>268.99</v>
       </c>
       <c r="AI10" t="n">
-        <v>4800</v>
+        <v>4881</v>
       </c>
       <c r="AJ10" t="n">
-        <v>9415.384615384615</v>
+        <v>9504</v>
       </c>
       <c r="AK10" t="n">
-        <v>9.486625000000036</v>
+        <v>9.484825000000036</v>
       </c>
       <c r="AL10" t="n">
-        <v>7.713028804294415</v>
+        <v>7.703314475105829</v>
       </c>
       <c r="AM10" t="n">
-        <v>7.770804522504227</v>
+        <v>7.770095484240271</v>
       </c>
       <c r="AN10" t="n">
-        <v>11.02405027167653</v>
+        <v>11.02087341121224</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.42866321706439</v>
+        <v>1.448618307857739</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.11623870651598</v>
+        <v>11.11567117846806</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7706666666666666</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.80664920385966</v>
+        <v>6.783256106042011</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9262786498040373</v>
       </c>
       <c r="AT10" t="n">
-        <v>17.83342091411231</v>
+        <v>17.77213099783007</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.06457212850356539</v>
+        <v>0.06433799709599017</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992351359158013</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.199863797070839</v>
+        <v>1.201918663240533</v>
       </c>
       <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
@@ -3691,49 +3691,49 @@
         <v>269.77</v>
       </c>
       <c r="BB10" t="n">
-        <v>6500</v>
+        <v>6480</v>
       </c>
       <c r="BC10" t="n">
-        <v>11115.38461538462</v>
+        <v>11104</v>
       </c>
       <c r="BD10" t="n">
         <v>4.810000000000002</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.270011258334289</v>
+        <v>4.2558583286573</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.273563857763413</v>
+        <v>4.274402753781993</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.051283060824218</v>
+        <v>6.05225976070539</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.4257562133370325</v>
+        <v>0.4260726306945508</v>
       </c>
       <c r="BI10" t="n">
-        <v>6.066242249977594</v>
+        <v>6.067238753970429</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7708333333333333</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.80664920385966</v>
+        <v>6.780340698135218</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9266769306898748</v>
       </c>
       <c r="BM10" t="n">
-        <v>17.83342091411231</v>
+        <v>17.76449262911427</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.03273998267056498</v>
+        <v>0.03261343875803042</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992325458578962</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202175477651729</v>
       </c>
       <c r="BQ10" t="inlineStr"/>
       <c r="BR10" t="inlineStr"/>
@@ -3744,49 +3744,49 @@
         <v>270.2</v>
       </c>
       <c r="BU10" t="n">
-        <v>6500</v>
+        <v>6480</v>
       </c>
       <c r="BV10" t="n">
-        <v>11115.38461538462</v>
+        <v>11106</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.23662500000001</v>
+        <v>5.23415000000001</v>
       </c>
       <c r="BX10" t="n">
-        <v>4.508922816863958</v>
+        <v>4.481840861918278</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.528138126810433</v>
+        <v>4.529548070742976</v>
       </c>
       <c r="BZ10" t="n">
-        <v>6.411957148108566</v>
+        <v>6.413760347172516</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.515222658491856</v>
+        <v>0.5162498061394977</v>
       </c>
       <c r="CB10" t="n">
-        <v>6.432623792590698</v>
+        <v>6.434503528113227</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7711666666666667</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.80664920385966</v>
+        <v>6.774515684235927</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9274737265426</v>
       </c>
       <c r="CF10" t="n">
-        <v>17.83342091411231</v>
+        <v>17.74923109269813</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.03564386938716167</v>
+        <v>0.03545883126864355</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992273446085906</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202689076994943</v>
       </c>
       <c r="CJ10" t="inlineStr"/>
       <c r="CK10" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
         <v>17.83814903173707</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.06458924830465776</v>
+        <v>0.06457699308776574</v>
       </c>
       <c r="CQ10" t="n">
         <v>3.948903220766222</v>
@@ -3820,13 +3820,13 @@
       </c>
       <c r="CX10" t="inlineStr"/>
       <c r="CY10" t="n">
-        <v>1.029084072557904</v>
+        <v>1.02637121244986</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.5536101791758975</v>
+        <v>0.5524710619578896</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.05595103714618</v>
+        <v>1.053099167267693</v>
       </c>
       <c r="DB10" t="inlineStr">
         <is>
@@ -3834,16 +3834,16 @@
         </is>
       </c>
       <c r="DC10" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297858533419857</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29757785467128</v>
       </c>
       <c r="DE10" t="n">
-        <v>1.299826689774697</v>
+        <v>1.297297297297297</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.299826689774697</v>
+        <v>1.296736546358332</v>
       </c>
     </row>
     <row r="11">
@@ -3905,49 +3905,49 @@
         <v>268.57</v>
       </c>
       <c r="P11" t="n">
-        <v>4700</v>
+        <v>4770</v>
       </c>
       <c r="Q11" t="n">
-        <v>9315.384615384615</v>
+        <v>9382</v>
       </c>
       <c r="R11" t="n">
-        <v>9.012000000000015</v>
+        <v>9.012600000000015</v>
       </c>
       <c r="S11" t="n">
-        <v>7.589700787973445</v>
+        <v>7.57689470974847</v>
       </c>
       <c r="T11" t="n">
-        <v>7.562621054090918</v>
+        <v>7.55140453407415</v>
       </c>
       <c r="U11" t="n">
-        <v>10.72438278779763</v>
+        <v>10.71142398303394</v>
       </c>
       <c r="V11" t="n">
-        <v>1.561865129429895</v>
+        <v>1.577711511906086</v>
       </c>
       <c r="W11" t="n">
-        <v>10.83751857492014</v>
+        <v>10.82699299709368</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7688333333333335</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.80664920385966</v>
+        <v>6.815453729254355</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9219027164999912</v>
       </c>
       <c r="AA11" t="n">
-        <v>17.83342091411231</v>
+        <v>17.85648877064641</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.06134152262518336</v>
+        <v>0.0614249582802779</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992631657802564</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.199863797070839</v>
+        <v>1.199093062865803</v>
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
@@ -3958,49 +3958,49 @@
         <v>268.99</v>
       </c>
       <c r="AI11" t="n">
-        <v>4800</v>
+        <v>4885</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9415.384615384615</v>
+        <v>9502</v>
       </c>
       <c r="AK11" t="n">
         <v>9.405000000000001</v>
       </c>
       <c r="AL11" t="n">
-        <v>7.648529647173817</v>
+        <v>7.638850198940554</v>
       </c>
       <c r="AM11" t="n">
-        <v>7.694005679415478</v>
+        <v>7.688076239403858</v>
       </c>
       <c r="AN11" t="n">
-        <v>10.91015345161025</v>
+        <v>10.90384939285952</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.660343388709633</v>
+        <v>1.658981699255216</v>
       </c>
       <c r="AP11" t="n">
-        <v>11.03576859607499</v>
+        <v>11.02933143307547</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7696666666666667</v>
       </c>
       <c r="AR11" t="n">
-        <v>6.80664920385966</v>
+        <v>6.800789267814117</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9238906044208459</v>
       </c>
       <c r="AT11" t="n">
-        <v>17.83342091411231</v>
+        <v>17.81806788167299</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.06401653576230011</v>
+        <v>0.06396142306379178</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992505291814564</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.199863797070839</v>
+        <v>1.200377571789752</v>
       </c>
       <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
@@ -4011,49 +4011,49 @@
         <v>269.77</v>
       </c>
       <c r="BB11" t="n">
-        <v>6500</v>
+        <v>6481</v>
       </c>
       <c r="BC11" t="n">
-        <v>11115.38461538462</v>
+        <v>11108</v>
       </c>
       <c r="BD11" t="n">
         <v>4.679999999999978</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.208029538591402</v>
+        <v>4.188823086977926</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.232413634891929</v>
+        <v>4.232987838248331</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.994004366084904</v>
+        <v>5.994627530441259</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.4165074893586085</v>
+        <v>0.4170419160703154</v>
       </c>
       <c r="BI11" t="n">
-        <v>6.008457941047496</v>
+        <v>6.009116672896597</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7713333333333333</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.80664920385966</v>
+        <v>6.771606075048078</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9278722414659917</v>
       </c>
       <c r="BM11" t="n">
-        <v>17.83342091411231</v>
+        <v>17.74160791662597</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.03185511827406306</v>
+        <v>0.03169111643122486</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992247333900647</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.199863797070839</v>
+        <v>1.202945861883308</v>
       </c>
       <c r="BQ11" t="inlineStr"/>
       <c r="BR11" t="inlineStr"/>
@@ -4064,49 +4064,49 @@
         <v>270.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>6500</v>
+        <v>6482</v>
       </c>
       <c r="BV11" t="n">
-        <v>11115.38461538462</v>
+        <v>11110</v>
       </c>
       <c r="BW11" t="n">
         <v>5.194999999999993</v>
       </c>
       <c r="BX11" t="n">
-        <v>4.440112917778618</v>
+        <v>4.406704192306141</v>
       </c>
       <c r="BY11" t="n">
-        <v>4.406550680851361</v>
+        <v>4.407963357662572</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.240463752562203</v>
+        <v>6.242157445986682</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.5814766837244281</v>
+        <v>0.5815110996988716</v>
       </c>
       <c r="CB11" t="n">
-        <v>6.267495750358184</v>
+        <v>6.269185333004597</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.7693333333333332</v>
+        <v>0.7715000000000001</v>
       </c>
       <c r="CD11" t="n">
-        <v>6.80664920385966</v>
+        <v>6.768698395574119</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.9230952145464986</v>
+        <v>0.9282708343583461</v>
       </c>
       <c r="CF11" t="n">
-        <v>17.83342091411231</v>
+        <v>17.73398979640419</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.03536054261405089</v>
+        <v>0.0351633881650075</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.9992556045629514</v>
+        <v>0.9992221150908543</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.199863797070839</v>
+        <v>1.203202636887033</v>
       </c>
       <c r="CJ11" t="inlineStr"/>
       <c r="CK11" t="inlineStr"/>
@@ -4140,13 +4140,13 @@
       </c>
       <c r="CX11" t="inlineStr"/>
       <c r="CY11" t="n">
-        <v>1.007751143403913</v>
+        <v>1.008176897207292</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.5501749660009879</v>
+        <v>0.5483577996540477</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.055152507143499</v>
+        <v>1.052014874059866</v>
       </c>
       <c r="DB11" t="inlineStr">
         <is>
@@ -4154,16 +4154,16 @@
         </is>
       </c>
       <c r="DC11" t="n">
-        <v>1.299826689774697</v>
+        <v>1.300672013873835</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.299826689774697</v>
+        <v>1.29926375054136</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.299826689774697</v>
+        <v>1.296456352636128</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.299826689774697</v>
+        <v>1.296176279974076</v>
       </c>
     </row>
   </sheetData>
